--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484654_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484654_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.2801</v>
+        <v>9.950200000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>9.124599999999999</v>
+        <v>9.042400000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1555</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>4.5252</v>
@@ -610,13 +610,13 @@
         <v>1.2828</v>
       </c>
       <c r="S2" t="n">
-        <v>0.954</v>
+        <v>0.624</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2557</v>
+        <v>0.1735</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6983</v>
+        <v>0.4506</v>
       </c>
       <c r="V2" t="n">
         <v>4.4344</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. RODRIGUEZ GIL</t>
+          <t>M. MORAGAS AZNAR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8746</v>
+        <v>4.6618</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7797</v>
+        <v>5.3383</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0949</v>
+        <v>-0.6765</v>
       </c>
       <c r="G3" t="n">
-        <v>0.061</v>
+        <v>0.3794</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4716</v>
+        <v>2.0591</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.4106</v>
+        <v>-1.6797</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1983</v>
+        <v>3.4386</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8393</v>
+        <v>3.3871</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.641</v>
+        <v>0.0515</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.1373</v>
+        <v>-3.0593</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3677</v>
+        <v>-1.3281</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7695</v>
+        <v>-1.7312</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.0995</v>
+        <v>2.0158</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6493</v>
+        <v>2.9321</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1672</v>
+        <v>0.3661</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2074</v>
+        <v>0.5935</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0402</v>
+        <v>-0.2274</v>
       </c>
       <c r="V3" t="n">
-        <v>4.7459</v>
+        <v>1.9005</v>
       </c>
       <c r="W3" t="n">
-        <v>4.1229</v>
+        <v>2.2224</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6231</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. MORAGAS AZNAR</t>
+          <t>J. SABATE PRATS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1557</v>
+        <v>3.9585</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9808</v>
+        <v>3.4911</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8250999999999999</v>
+        <v>0.4674</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3794</v>
+        <v>4.6092</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0591</v>
+        <v>2.2468</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.6797</v>
+        <v>2.3624</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4386</v>
+        <v>5.3116</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3871</v>
+        <v>3.2695</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0515</v>
+        <v>2.042</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.0593</v>
+        <v>-0.7024</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3281</v>
+        <v>-1.0228</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.7312</v>
+        <v>0.3204</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0158</v>
+        <v>-2.3823</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9321</v>
+        <v>1.2828</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.14</v>
+        <v>-0.1687</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2361</v>
+        <v>-0.0558</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.376</v>
+        <v>-0.113</v>
       </c>
       <c r="V4" t="n">
         <v>1.9005</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2224</v>
+        <v>1.9005</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. SABATE PRATS</t>
+          <t>V. RODRIGUEZ GIL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9931</v>
+        <v>3.7397</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9964</v>
+        <v>3.8182</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0785</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6092</v>
+        <v>0.061</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2468</v>
+        <v>1.4716</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3624</v>
+        <v>-1.4106</v>
       </c>
       <c r="J5" t="n">
-        <v>5.3116</v>
+        <v>2.1983</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2695</v>
+        <v>2.8393</v>
       </c>
       <c r="L5" t="n">
-        <v>2.042</v>
+        <v>-0.641</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7024</v>
+        <v>-2.1373</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0228</v>
+        <v>-1.3677</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3204</v>
+        <v>-0.7695</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.3823</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.6651</v>
+        <v>-2.7489</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1342</v>
+        <v>0.0322</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5505</v>
+        <v>0.2459</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5836</v>
+        <v>-0.2136</v>
       </c>
       <c r="V5" t="n">
-        <v>1.9005</v>
+        <v>4.7459</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9005</v>
+        <v>4.1229</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.313</v>
+        <v>1.3651</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7391</v>
+        <v>0.8903</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5739</v>
+        <v>0.4748</v>
       </c>
       <c r="G6" t="n">
         <v>0.4696</v>
@@ -922,13 +922,13 @@
         <v>1.0995</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.526</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4404</v>
+        <v>-0.2892</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1377</v>
+        <v>-0.2368</v>
       </c>
       <c r="V6" t="n">
         <v>0.3219</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CAMPOS DE BENGOA</t>
+          <t>M. NOS BARBERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2291</v>
+        <v>-1.2879</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.454</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7751</v>
+        <v>-0.5677</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.1047</v>
+        <v>-1.3154</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0404</v>
+        <v>0.8001</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0643</v>
+        <v>-2.1155</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5278</v>
+        <v>-0.6102</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5793</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0515</v>
+        <v>-1.2821</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5769</v>
+        <v>-0.7053</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4611</v>
+        <v>0.1282</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1158</v>
+        <v>-0.8335</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0995</v>
+        <v>0.1833</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0158</v>
+        <v>0.1833</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3992</v>
+        <v>-0.1557</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3462</v>
+        <v>-0.1101</v>
       </c>
       <c r="U8" t="n">
-        <v>1.053</v>
+        <v>-0.0456</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. NOS BARBERA</t>
+          <t>J. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3375</v>
+        <v>-1.3452</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.0004</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6172</v>
+        <v>-1.3449</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3154</v>
+        <v>-3.1047</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8001</v>
+        <v>-1.0404</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1155</v>
+        <v>-2.0643</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6102</v>
+        <v>-0.5278</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6719000000000001</v>
+        <v>-0.5793</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2821</v>
+        <v>0.0515</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7053</v>
+        <v>-2.5769</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1282</v>
+        <v>-0.4611</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8335</v>
+        <v>-2.1158</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1833</v>
+        <v>1.0995</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1833</v>
+        <v>2.0158</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2053</v>
+        <v>1.283</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1101</v>
+        <v>0.7998</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.4832</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. IGBINS DAVID</t>
+          <t>M. MARIA VENTURA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4761</v>
+        <v>-1.7401</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.516</v>
+        <v>0.5264</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0399</v>
+        <v>-2.2664</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0364</v>
+        <v>-0.295</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6322</v>
+        <v>-0.029</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4042</v>
+        <v>-0.266</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2701</v>
+        <v>1.311</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4368</v>
+        <v>0.5511</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1667</v>
+        <v>0.76</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7664</v>
+        <v>-1.606</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1955</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5709</v>
+        <v>-1.0259</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0158</v>
+        <v>1.4661</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6493</v>
+        <v>2.3823</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>-0.0552</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0973</v>
+        <v>0.1316</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2327</v>
+        <v>-0.1869</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2461</v>
+        <v>-2.8559</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.9242</v>
+        <v>-2.8559</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0568</v>
+        <v>-1.7872</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6058</v>
+        <v>-0.5097</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4509</v>
+        <v>-1.2775</v>
       </c>
       <c r="G11" t="n">
         <v>-3.3474</v>
@@ -1312,13 +1312,13 @@
         <v>1.4661</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5262</v>
+        <v>-0.2566</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0196</v>
+        <v>0.0766</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5066000000000001</v>
+        <v>-0.3332</v>
       </c>
       <c r="V11" t="n">
         <v>1.267</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. MARIA VENTURA</t>
+          <t>A. IGBINS DAVID</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2739</v>
+        <v>-2.1327</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2651</v>
+        <v>-3.0239</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5389</v>
+        <v>0.8912</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.295</v>
+        <v>-2.0364</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.029</v>
+        <v>-0.6322</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.266</v>
+        <v>-1.4042</v>
       </c>
       <c r="J12" t="n">
-        <v>1.311</v>
+        <v>-0.2701</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5511</v>
+        <v>-0.4368</v>
       </c>
       <c r="L12" t="n">
-        <v>0.76</v>
+        <v>0.1667</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.606</v>
+        <v>-1.7664</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.1955</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0259</v>
+        <v>-1.5709</v>
       </c>
       <c r="P12" t="n">
-        <v>1.4661</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3823</v>
+        <v>1.6493</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5891</v>
+        <v>0.6735</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1297</v>
+        <v>0.5894</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4594</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.8559</v>
+        <v>1.2461</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.8559</v>
+        <v>0.9242</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.3452</v>
+        <v>-4.3831</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.0254</v>
+        <v>-2.1872</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3197</v>
+        <v>-2.1959</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9978</v>
@@ -1468,13 +1468,13 @@
         <v>2.3823</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.486</v>
+        <v>0.4761</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3499</v>
+        <v>0.4883</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1361</v>
+        <v>-0.0123</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5785</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.8732</v>
+        <v>11.9744</v>
       </c>
       <c r="E14" t="n">
-        <v>16.5395</v>
+        <v>17.6405</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.666</v>
+        <v>-5.6662</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.077</v>
+        <v>-1.076999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>7.097300000000002</v>
+        <v>7.097300000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.174199999999999</v>
+        <v>-8.174200000000001</v>
       </c>
       <c r="J14" t="n">
         <v>16.8001</v>
@@ -1525,7 +1525,7 @@
         <v>15.9968</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8030000000000002</v>
+        <v>0.803</v>
       </c>
       <c r="M14" t="n">
         <v>-17.8771</v>
@@ -1537,7 +1537,7 @@
         <v>-8.9772</v>
       </c>
       <c r="P14" t="n">
-        <v>0.000100000000000211</v>
+        <v>9.999999999976694e-05</v>
       </c>
       <c r="Q14" t="n">
         <v>-18.3257</v>
@@ -1546,13 +1546,13 @@
         <v>18.3256</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1915</v>
+        <v>2.2927</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5425</v>
+        <v>2.6435</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3507999999999999</v>
+        <v>-0.3509</v>
       </c>
       <c r="V14" t="n">
         <v>10.7588</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6933</v>
+        <v>3.5854</v>
       </c>
       <c r="E15" t="n">
-        <v>2.514</v>
+        <v>2.8025</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1793</v>
+        <v>0.7829</v>
       </c>
       <c r="G15" t="n">
         <v>3.1458</v>
@@ -1624,13 +1624,13 @@
         <v>1.8326</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2508</v>
+        <v>0.1429</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4962</v>
+        <v>-0.2077</v>
       </c>
       <c r="U15" t="n">
-        <v>0.747</v>
+        <v>0.3506</v>
       </c>
       <c r="V15" t="n">
         <v>1.213</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6255</v>
+        <v>2.455</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9648</v>
+        <v>1.8687</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6607</v>
+        <v>0.5864</v>
       </c>
       <c r="G16" t="n">
         <v>5.1966</v>
@@ -1702,13 +1702,13 @@
         <v>2.3823</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0669</v>
+        <v>-0.2374</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1079</v>
+        <v>0.0117</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1748</v>
+        <v>-0.2491</v>
       </c>
       <c r="V16" t="n">
         <v>-1.9544</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7292</v>
+        <v>2.2407</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1502</v>
+        <v>2.4387</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.421</v>
+        <v>-0.198</v>
       </c>
       <c r="G17" t="n">
         <v>1.2183</v>
@@ -1780,13 +1780,13 @@
         <v>1.8326</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1523</v>
+        <v>-0.6408</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4042</v>
+        <v>-0.1157</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7481</v>
+        <v>-0.5251</v>
       </c>
       <c r="V17" t="n">
         <v>1.8465</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1374</v>
+        <v>1.2088</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1333</v>
+        <v>1.2295</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0041</v>
+        <v>-0.0206</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0368</v>
@@ -1858,13 +1858,13 @@
         <v>0.733</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.6959</v>
       </c>
       <c r="T18" t="n">
-        <v>0.494</v>
+        <v>0.5901</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1305</v>
+        <v>0.1058</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1346</v>
+        <v>0.3824</v>
       </c>
       <c r="E20" t="n">
         <v>2.4469</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3122</v>
+        <v>-2.0645</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1182</v>
@@ -2014,13 +2014,13 @@
         <v>2.3823</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5694</v>
+        <v>-0.3216</v>
       </c>
       <c r="T20" t="n">
         <v>-0.07539999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.494</v>
+        <v>-0.2462</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6439</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0296</v>
+        <v>-0.5488</v>
       </c>
       <c r="E21" t="n">
-        <v>0.989</v>
+        <v>1.4698</v>
       </c>
       <c r="F21" t="n">
         <v>-2.0186</v>
@@ -2092,10 +2092,10 @@
         <v>0.9163</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4947</v>
+        <v>-0.0139</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3122</v>
+        <v>0.1686</v>
       </c>
       <c r="U21" t="n">
         <v>-0.1825</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1513</v>
+        <v>-0.7885</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3863</v>
+        <v>-1.0978</v>
       </c>
       <c r="F22" t="n">
-        <v>0.235</v>
+        <v>0.3093</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8788</v>
@@ -2170,13 +2170,13 @@
         <v>2.1991</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4271</v>
+        <v>-0.0643</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.368</v>
+        <v>-0.0795</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0591</v>
+        <v>0.0153</v>
       </c>
       <c r="V22" t="n">
         <v>-0.945</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5902</v>
+        <v>-2.9005</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3072</v>
+        <v>-0.0775</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8973</v>
+        <v>-2.823</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8763</v>
@@ -2248,13 +2248,13 @@
         <v>2.1991</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2438</v>
+        <v>-0.5541</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7308</v>
+        <v>0.3462</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9746</v>
+        <v>-0.9003</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6533</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9725</v>
+        <v>-3.8516</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1745</v>
+        <v>-1.0783</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7981</v>
+        <v>-2.7733</v>
       </c>
       <c r="G24" t="n">
         <v>-1.2614</v>
@@ -2326,13 +2326,13 @@
         <v>1.8326</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7716</v>
+        <v>-0.6506</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5875</v>
+        <v>-0.4913</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1841</v>
+        <v>-0.1593</v>
       </c>
       <c r="V24" t="n">
         <v>-2.8559</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.1481</v>
+        <v>-5.1977</v>
       </c>
       <c r="E25" t="n">
         <v>-3.0967</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0515</v>
+        <v>-2.101</v>
       </c>
       <c r="G25" t="n">
         <v>-0.9891</v>
@@ -2404,13 +2404,13 @@
         <v>0.733</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0401</v>
+        <v>-0.0094</v>
       </c>
       <c r="T25" t="n">
         <v>-0.2021</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2422</v>
+        <v>0.1927</v>
       </c>
       <c r="V25" t="n">
         <v>-1.267</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.927</v>
+        <v>-8.0838</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-1.8647</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.12</v>
+        <v>-6.2191</v>
       </c>
       <c r="G26" t="n">
         <v>-4.7641</v>
@@ -2482,13 +2482,13 @@
         <v>1.2828</v>
       </c>
       <c r="S26" t="n">
-        <v>1.6187</v>
+        <v>0.4619</v>
       </c>
       <c r="T26" t="n">
-        <v>1.4638</v>
+        <v>0.4061</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1549</v>
+        <v>0.0558</v>
       </c>
       <c r="V26" t="n">
         <v>-3.2318</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-10.8736</v>
+        <v>-10.8735</v>
       </c>
       <c r="E27" t="n">
-        <v>5.665999999999999</v>
+        <v>5.666199999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-16.5396</v>
+        <v>-16.5395</v>
       </c>
       <c r="G27" t="n">
         <v>1.076899999999998</v>
@@ -2560,13 +2560,13 @@
         <v>18.3257</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.1917</v>
+        <v>-1.1914</v>
       </c>
       <c r="T27" t="n">
-        <v>0.3509</v>
+        <v>0.3509999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.5426</v>
+        <v>-1.5423</v>
       </c>
       <c r="V27" t="n">
         <v>-10.7588</v>
